--- a/artfynd/A 50236-2022 artfynd.xlsx
+++ b/artfynd/A 50236-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50236-2022 artfynd.xlsx
+++ b/artfynd/A 50236-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>94540240</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404331.6916097297</v>
+        <v>404332</v>
       </c>
       <c r="R2" t="n">
-        <v>6713729.20438577</v>
+        <v>6713729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>94540246</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404352.5299800595</v>
+        <v>404352</v>
       </c>
       <c r="R3" t="n">
-        <v>6713678.449803685</v>
+        <v>6713679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>78757146</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>404306</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6713554</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50236-2022 artfynd.xlsx
+++ b/artfynd/A 50236-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540240</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540246</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,8 +983,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78757146</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>